--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,120 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128744962</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98563</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skogsbilväg NV Lenbergsvik, Glans kalkbarrskogar, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>549372</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6497427</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98566</v>
+        <v>98567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98567</v>
+        <v>98594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98594</v>
+        <v>98600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98600</v>
+        <v>98607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98607</v>
+        <v>98611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98611</v>
+        <v>98618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98626</v>
+        <v>98631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98631</v>
+        <v>98634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98634</v>
+        <v>98644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128744962</v>
       </c>
       <c r="B3" t="n">
-        <v>98644</v>
+        <v>98653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -675,63 +675,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112134362</v>
+        <v>128744962</v>
       </c>
       <c r="B2" t="n">
-        <v>90897</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>219797</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jakobslund (Jakobslund), Ög</t>
+          <t>Skogsbilväg NV Lenbergsvik, Glans kalkbarrskogar, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549312</v>
+        <v>549372</v>
       </c>
       <c r="R2" t="n">
-        <v>6497467</v>
+        <v>6497427</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:39</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:39</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,82 +770,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Nilsson</t>
+          <t>Robert Petersen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Nilsson</t>
+          <t>Robert Petersen, Tilda Lindkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128744962</v>
+        <v>122712634</v>
       </c>
       <c r="B3" t="n">
-        <v>98653</v>
+        <v>91402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219797</v>
+        <v>256703</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogsbilväg NV Lenbergsvik, Glans kalkbarrskogar, Ög</t>
+          <t>Smittebo, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549372</v>
+        <v>549443</v>
       </c>
       <c r="R3" t="n">
-        <v>6497427</v>
+        <v>6497360</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,12 +878,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Robert Petersen</t>
+          <t>Martin Gotink</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Robert Petersen, Tilda Lindkvist</t>
+          <t>Martin Gotink</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 55022-2022 artfynd.xlsx
+++ b/artfynd/A 55022-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744962</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,8 +897,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122712634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>